--- a/order_forms/016_trade_show_sample_refill_order_form--order_forms.xlsx
+++ b/order_forms/016_trade_show_sample_refill_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1014,8 +1014,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'ground'}</t>
+          <t>ground</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Ground'}</t>
+          <t>Ground</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'air'}</t>
+          <t>air</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Air'}</t>
+          <t>Air</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'ship_to_1'}</t>
+          <t>ship_to_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Ship To 1'}</t>
+          <t>Ship To 1</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ship_to_2'}</t>
+          <t>ship_to_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Ship To 2'}</t>
+          <t>Ship To 2</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'ship_to_3'}</t>
+          <t>ship_to_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Ship To 3'}</t>
+          <t>Ship To 3</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
